--- a/dpp-textile-jbl/data/SIMULATED_responses.xlsx
+++ b/dpp-textile-jbl/data/SIMULATED_responses.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="259">
   <si>
     <t>firm</t>
   </si>
@@ -55,7 +55,7 @@
     <t>B6</t>
   </si>
   <si>
-    <t>CERT</t>
+    <t>B7</t>
   </si>
   <si>
     <t>VI_1</t>
@@ -490,21 +490,21 @@
     <t>2027-02-24</t>
   </si>
   <si>
+    <t>Head of merchandising/sourcing</t>
+  </si>
+  <si>
+    <t>Head of compliance/sustainability</t>
+  </si>
+  <si>
     <t>Owner/MD/Director</t>
   </si>
   <si>
-    <t>Head of compliance/sustainability</t>
-  </si>
-  <si>
-    <t>Head of merchandising/sourcing</t>
+    <t>Directly responsible</t>
   </si>
   <si>
     <t>Somewhat</t>
   </si>
   <si>
-    <t>Directly responsible</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -526,115 +526,112 @@
     <t>Panipat</t>
   </si>
   <si>
-    <t>GRS/RCS; ISO 14001; Better Cotton</t>
-  </si>
-  <si>
-    <t>Better Cotton; ISO 14001; GRS/RCS; ZDHC; Higg FEM verified</t>
-  </si>
-  <si>
-    <t>Higg FEM verified; GOTS; GRS/RCS; ISO 14001</t>
-  </si>
-  <si>
-    <t>ZDHC; Better Cotton; GRS/RCS; Higg FEM verified; OEKO-TEX; GOTS</t>
-  </si>
-  <si>
-    <t>GRS/RCS; GOTS; Better Cotton; Higg FEM verified</t>
-  </si>
-  <si>
-    <t>bluesign; GOTS; GRS/RCS; ISO 14001</t>
-  </si>
-  <si>
-    <t>OEKO-TEX; Better Cotton; ISO 14001; ZDHC</t>
-  </si>
-  <si>
-    <t>GOTS; bluesign; GRS/RCS; Higg FEM verified</t>
-  </si>
-  <si>
-    <t>ISO 14001; ZDHC; OEKO-TEX; Higg FEM verified</t>
-  </si>
-  <si>
-    <t>GOTS; GRS/RCS; bluesign</t>
-  </si>
-  <si>
-    <t>GOTS; bluesign</t>
-  </si>
-  <si>
-    <t>GOTS; GRS/RCS; ZDHC</t>
-  </si>
-  <si>
-    <t>Better Cotton; ZDHC</t>
-  </si>
-  <si>
-    <t>OEKO-TEX; GOTS</t>
-  </si>
-  <si>
-    <t>GOTS; ISO 14001</t>
+    <t>GRS/RCS; OEKO-TEX; ISO 14001</t>
+  </si>
+  <si>
+    <t>OCS; OEKO-TEX; bluesign; GRS/RCS; ISO 14001; Better Cotton</t>
+  </si>
+  <si>
+    <t>Better Cotton; GOTS; Higg FEM verified</t>
+  </si>
+  <si>
+    <t>OEKO-TEX; Higg FEM verified; ZDHC</t>
+  </si>
+  <si>
+    <t>ISO 14001; GOTS; OCS</t>
+  </si>
+  <si>
+    <t>ZDHC; OCS; GOTS; GRS/RCS</t>
+  </si>
+  <si>
+    <t>bluesign; OCS; Higg FEM verified; GOTS</t>
+  </si>
+  <si>
+    <t>ISO 14001; Higg FEM verified; Better Cotton; OEKO-TEX</t>
+  </si>
+  <si>
+    <t>GOTS; Better Cotton; GRS/RCS; ISO 14001</t>
   </si>
   <si>
     <t>GOTS</t>
   </si>
   <si>
-    <t>GOTS; Better Cotton</t>
-  </si>
-  <si>
-    <t>bluesign; OEKO-TEX</t>
-  </si>
-  <si>
-    <t>OEKO-TEX; GRS/RCS</t>
-  </si>
-  <si>
-    <t>Better Cotton; GRS/RCS</t>
+    <t>GRS/RCS</t>
+  </si>
+  <si>
+    <t>Higg FEM verified</t>
+  </si>
+  <si>
+    <t>GOTS; OCS; ZDHC</t>
+  </si>
+  <si>
+    <t>bluesign; GRS/RCS</t>
+  </si>
+  <si>
+    <t>OEKO-TEX</t>
+  </si>
+  <si>
+    <t>GOTS; GRS/RCS</t>
+  </si>
+  <si>
+    <t>ISO 14001</t>
+  </si>
+  <si>
+    <t>GOTS; Higg FEM verified</t>
+  </si>
+  <si>
+    <t>ZDHC; Higg FEM verified</t>
+  </si>
+  <si>
+    <t>GRS/RCS; Higg FEM verified</t>
+  </si>
+  <si>
+    <t>OCS; ZDHC</t>
+  </si>
+  <si>
+    <t>bluesign; OCS</t>
+  </si>
+  <si>
+    <t>ZDHC; OCS; Higg FEM verified</t>
+  </si>
+  <si>
+    <t>bluesign</t>
+  </si>
+  <si>
+    <t>GOTS; ZDHC; OCS</t>
   </si>
   <si>
     <t>ZDHC</t>
   </si>
   <si>
-    <t>Better Cotton</t>
-  </si>
-  <si>
-    <t>OEKO-TEX</t>
-  </si>
-  <si>
-    <t>bluesign; OEKO-TEX; ZDHC</t>
-  </si>
-  <si>
-    <t>bluesign</t>
-  </si>
-  <si>
-    <t>Better Cotton; Higg FEM verified; GOTS</t>
-  </si>
-  <si>
-    <t>ZDHC; bluesign</t>
-  </si>
-  <si>
-    <t>GRS/RCS</t>
-  </si>
-  <si>
-    <t>GRS/RCS; OEKO-TEX; Higg FEM verified; ZDHC; Better Cotton</t>
+    <t>OCS</t>
   </si>
   <si>
     <t>GRS/RCS; GOTS; Better Cotton</t>
   </si>
   <si>
-    <t>Better Cotton; ISO 14001; GRS/RCS; OEKO-TEX</t>
-  </si>
-  <si>
-    <t>Better Cotton; Higg FEM verified; GRS/RCS; OEKO-TEX; GOTS</t>
-  </si>
-  <si>
-    <t>GRS/RCS; OEKO-TEX; Higg FEM verified; ISO 14001</t>
-  </si>
-  <si>
-    <t>GRS/RCS; Higg FEM verified; bluesign</t>
-  </si>
-  <si>
-    <t>bluesign; ISO 14001; Higg FEM verified; GRS/RCS</t>
-  </si>
-  <si>
-    <t>Higg FEM verified; GRS/RCS; ISO 14001</t>
-  </si>
-  <si>
-    <t>ISO 14001; Better Cotton; OEKO-TEX</t>
+    <t>GRS/RCS; Better Cotton; bluesign; GOTS</t>
+  </si>
+  <si>
+    <t>Better Cotton; GRS/RCS; OEKO-TEX</t>
+  </si>
+  <si>
+    <t>GOTS; Better Cotton; OCS; GRS/RCS; ISO 14001</t>
+  </si>
+  <si>
+    <t>GRS/RCS; ISO 14001; OEKO-TEX; Higg FEM verified; OCS</t>
+  </si>
+  <si>
+    <t>OEKO-TEX; GRS/RCS; GOTS</t>
+  </si>
+  <si>
+    <t>Better Cotton; ZDHC; OEKO-TEX</t>
+  </si>
+  <si>
+    <t>OEKO-TEX; Better Cotton; ZDHC</t>
+  </si>
+  <si>
+    <t>OCS; OEKO-TEX</t>
   </si>
   <si>
     <t>N</t>
@@ -1297,7 +1294,7 @@
         <v>158</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="G2" t="s">
         <v>161</v>
@@ -1306,13 +1303,13 @@
         <v>163</v>
       </c>
       <c r="I2">
-        <v>4668</v>
+        <v>6887</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L2" t="s">
         <v>164</v>
@@ -1321,40 +1318,40 @@
         <v>170</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="O2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z2">
         <v>9</v>
@@ -1369,67 +1366,67 @@
         <v>2</v>
       </c>
       <c r="AD2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN2">
+        <v>4</v>
+      </c>
+      <c r="AO2">
+        <v>3</v>
+      </c>
+      <c r="AP2">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV2" t="s">
         <v>208</v>
       </c>
-      <c r="AH2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN2">
-        <v>3</v>
-      </c>
-      <c r="AO2">
-        <v>4</v>
-      </c>
-      <c r="AP2">
-        <v>4</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>208</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>207</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>209</v>
-      </c>
       <c r="AW2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:50">
@@ -1446,25 +1443,25 @@
         <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H3" t="s">
         <v>163</v>
       </c>
       <c r="I3">
-        <v>9130</v>
+        <v>19129</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="L3" t="s">
         <v>165</v>
@@ -1473,55 +1470,55 @@
         <v>171</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="O3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y3" t="s">
         <v>207</v>
       </c>
       <c r="Z3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA3">
+        <v>14</v>
+      </c>
+      <c r="AB3">
         <v>12</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <v>10</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>7</v>
-      </c>
-      <c r="AD3">
-        <v>6</v>
       </c>
       <c r="AE3">
         <v>5</v>
@@ -1530,58 +1527,58 @@
         <v>7</v>
       </c>
       <c r="AG3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK3" t="s">
         <v>207</v>
       </c>
       <c r="AL3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AU3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AV3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AW3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AX3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:50">
@@ -1598,25 +1595,25 @@
         <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H4" t="s">
         <v>163</v>
       </c>
       <c r="I4">
-        <v>3960</v>
+        <v>17134</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L4" t="s">
         <v>165</v>
@@ -1625,40 +1622,40 @@
         <v>172</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="O4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="T4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z4">
         <v>7</v>
@@ -1667,73 +1664,73 @@
         <v>4</v>
       </c>
       <c r="AB4">
+        <v>3</v>
+      </c>
+      <c r="AC4">
+        <v>2</v>
+      </c>
+      <c r="AD4">
         <v>4</v>
       </c>
-      <c r="AC4">
+      <c r="AE4">
+        <v>5</v>
+      </c>
+      <c r="AF4">
+        <v>6</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN4">
+        <v>2</v>
+      </c>
+      <c r="AO4">
         <v>3</v>
       </c>
-      <c r="AD4">
-        <v>7</v>
-      </c>
-      <c r="AE4">
-        <v>6</v>
-      </c>
-      <c r="AF4">
-        <v>5</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>208</v>
-      </c>
-      <c r="AN4">
-        <v>3</v>
-      </c>
-      <c r="AO4">
-        <v>4</v>
-      </c>
       <c r="AP4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AU4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AV4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AW4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AX4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:50">
@@ -1750,10 +1747,10 @@
         <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G5" t="s">
         <v>162</v>
@@ -1762,13 +1759,13 @@
         <v>163</v>
       </c>
       <c r="I5">
-        <v>2524</v>
+        <v>10734</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L5" t="s">
         <v>166</v>
@@ -1777,34 +1774,34 @@
         <v>173</v>
       </c>
       <c r="N5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="T5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X5" t="s">
         <v>207</v>
@@ -1813,79 +1810,79 @@
         <v>207</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AA5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
         <v>7</v>
       </c>
       <c r="AF5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AG5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL5" t="s">
         <v>207</v>
       </c>
       <c r="AM5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP5">
         <v>2</v>
       </c>
       <c r="AQ5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>206</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>206</v>
+      </c>
+      <c r="AV5" t="s">
         <v>208</v>
       </c>
-      <c r="AR5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>208</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>207</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>209</v>
-      </c>
       <c r="AW5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:50">
@@ -1905,7 +1902,7 @@
         <v>160</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
         <v>161</v>
@@ -1914,13 +1911,13 @@
         <v>163</v>
       </c>
       <c r="I6">
-        <v>7587</v>
+        <v>16798</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="L6" t="s">
         <v>164</v>
@@ -1929,82 +1926,82 @@
         <v>174</v>
       </c>
       <c r="N6">
+        <v>67</v>
+      </c>
+      <c r="O6" t="s">
+        <v>206</v>
+      </c>
+      <c r="P6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>207</v>
+      </c>
+      <c r="R6" t="s">
+        <v>207</v>
+      </c>
+      <c r="S6" t="s">
+        <v>207</v>
+      </c>
+      <c r="T6" t="s">
+        <v>207</v>
+      </c>
+      <c r="U6" t="s">
+        <v>207</v>
+      </c>
+      <c r="V6" t="s">
+        <v>207</v>
+      </c>
+      <c r="W6" t="s">
+        <v>207</v>
+      </c>
+      <c r="X6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z6">
+        <v>11</v>
+      </c>
+      <c r="AA6">
+        <v>8</v>
+      </c>
+      <c r="AB6">
+        <v>7</v>
+      </c>
+      <c r="AC6">
+        <v>5</v>
+      </c>
+      <c r="AD6">
         <v>4</v>
       </c>
-      <c r="O6" t="s">
-        <v>208</v>
-      </c>
-      <c r="P6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>208</v>
-      </c>
-      <c r="R6" t="s">
-        <v>208</v>
-      </c>
-      <c r="S6" t="s">
-        <v>208</v>
-      </c>
-      <c r="T6" t="s">
-        <v>208</v>
-      </c>
-      <c r="U6" t="s">
-        <v>208</v>
-      </c>
-      <c r="V6" t="s">
-        <v>208</v>
-      </c>
-      <c r="W6" t="s">
-        <v>208</v>
-      </c>
-      <c r="X6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z6">
-        <v>4</v>
-      </c>
-      <c r="AA6">
-        <v>3</v>
-      </c>
-      <c r="AB6">
-        <v>2</v>
-      </c>
-      <c r="AC6">
-        <v>2</v>
-      </c>
-      <c r="AD6">
-        <v>7</v>
-      </c>
       <c r="AE6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN6">
         <v>2</v>
@@ -2013,31 +2010,31 @@
         <v>3</v>
       </c>
       <c r="AP6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU6" t="s">
         <v>207</v>
       </c>
       <c r="AV6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AW6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AX6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:50">
@@ -2054,25 +2051,25 @@
         <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H7" t="s">
         <v>163</v>
       </c>
       <c r="I7">
-        <v>11695</v>
+        <v>21250</v>
       </c>
       <c r="J7">
         <v>1</v>
       </c>
       <c r="K7">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="L7" t="s">
         <v>164</v>
@@ -2081,115 +2078,115 @@
         <v>175</v>
       </c>
       <c r="N7">
+        <v>44</v>
+      </c>
+      <c r="O7" t="s">
+        <v>206</v>
+      </c>
+      <c r="P7" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>207</v>
+      </c>
+      <c r="R7" t="s">
+        <v>207</v>
+      </c>
+      <c r="S7" t="s">
+        <v>206</v>
+      </c>
+      <c r="T7" t="s">
+        <v>207</v>
+      </c>
+      <c r="U7" t="s">
+        <v>207</v>
+      </c>
+      <c r="V7" t="s">
+        <v>207</v>
+      </c>
+      <c r="W7" t="s">
+        <v>207</v>
+      </c>
+      <c r="X7" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z7">
+        <v>8</v>
+      </c>
+      <c r="AA7">
+        <v>6</v>
+      </c>
+      <c r="AB7">
+        <v>5</v>
+      </c>
+      <c r="AC7">
         <v>4</v>
       </c>
-      <c r="O7" t="s">
-        <v>207</v>
-      </c>
-      <c r="P7" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>208</v>
-      </c>
-      <c r="R7" t="s">
-        <v>208</v>
-      </c>
-      <c r="S7" t="s">
-        <v>208</v>
-      </c>
-      <c r="T7" t="s">
-        <v>208</v>
-      </c>
-      <c r="U7" t="s">
-        <v>208</v>
-      </c>
-      <c r="V7" t="s">
-        <v>208</v>
-      </c>
-      <c r="W7" t="s">
-        <v>208</v>
-      </c>
-      <c r="X7" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z7">
-        <v>16</v>
-      </c>
-      <c r="AA7">
-        <v>13</v>
-      </c>
-      <c r="AB7">
-        <v>11</v>
-      </c>
-      <c r="AC7">
-        <v>9</v>
-      </c>
       <c r="AD7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ7" t="s">
         <v>207</v>
       </c>
       <c r="AK7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AL7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AN7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO7">
         <v>3</v>
       </c>
       <c r="AP7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AU7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AV7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AW7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AX7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:50">
@@ -2206,25 +2203,25 @@
         <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H8" t="s">
         <v>163</v>
       </c>
       <c r="I8">
-        <v>23815</v>
+        <v>1559</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L8" t="s">
         <v>165</v>
@@ -2233,85 +2230,85 @@
         <v>176</v>
       </c>
       <c r="N8">
+        <v>39</v>
+      </c>
+      <c r="O8" t="s">
+        <v>206</v>
+      </c>
+      <c r="P8" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>207</v>
+      </c>
+      <c r="R8" t="s">
+        <v>207</v>
+      </c>
+      <c r="S8" t="s">
+        <v>206</v>
+      </c>
+      <c r="T8" t="s">
+        <v>207</v>
+      </c>
+      <c r="U8" t="s">
+        <v>207</v>
+      </c>
+      <c r="V8" t="s">
+        <v>207</v>
+      </c>
+      <c r="W8" t="s">
+        <v>207</v>
+      </c>
+      <c r="X8" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z8">
+        <v>7</v>
+      </c>
+      <c r="AA8">
+        <v>6</v>
+      </c>
+      <c r="AB8">
+        <v>5</v>
+      </c>
+      <c r="AC8">
         <v>4</v>
       </c>
-      <c r="O8" t="s">
-        <v>208</v>
-      </c>
-      <c r="P8" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>208</v>
-      </c>
-      <c r="R8" t="s">
-        <v>208</v>
-      </c>
-      <c r="S8" t="s">
-        <v>208</v>
-      </c>
-      <c r="T8" t="s">
-        <v>208</v>
-      </c>
-      <c r="U8" t="s">
-        <v>208</v>
-      </c>
-      <c r="V8" t="s">
-        <v>208</v>
-      </c>
-      <c r="W8" t="s">
-        <v>208</v>
-      </c>
-      <c r="X8" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z8">
-        <v>13</v>
-      </c>
-      <c r="AA8">
-        <v>9</v>
-      </c>
-      <c r="AB8">
-        <v>8</v>
-      </c>
-      <c r="AC8">
-        <v>6</v>
-      </c>
       <c r="AD8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF8">
         <v>5</v>
       </c>
       <c r="AG8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AN8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
         <v>4</v>
@@ -2320,28 +2317,28 @@
         <v>3</v>
       </c>
       <c r="AQ8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>207</v>
+      </c>
+      <c r="AV8" t="s">
         <v>208</v>
       </c>
-      <c r="AR8" t="s">
-        <v>208</v>
-      </c>
-      <c r="AS8" t="s">
-        <v>208</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>207</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>207</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>209</v>
-      </c>
       <c r="AW8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AX8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:50">
@@ -2358,10 +2355,10 @@
         <v>115</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
         <v>161</v>
@@ -2370,13 +2367,13 @@
         <v>163</v>
       </c>
       <c r="I9">
-        <v>7465</v>
+        <v>8061</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="L9" t="s">
         <v>165</v>
@@ -2385,115 +2382,115 @@
         <v>177</v>
       </c>
       <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>206</v>
+      </c>
+      <c r="P9" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>207</v>
+      </c>
+      <c r="R9" t="s">
+        <v>207</v>
+      </c>
+      <c r="S9" t="s">
+        <v>207</v>
+      </c>
+      <c r="T9" t="s">
+        <v>207</v>
+      </c>
+      <c r="U9" t="s">
+        <v>207</v>
+      </c>
+      <c r="V9" t="s">
+        <v>207</v>
+      </c>
+      <c r="W9" t="s">
+        <v>207</v>
+      </c>
+      <c r="X9" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z9">
+        <v>5</v>
+      </c>
+      <c r="AA9">
         <v>4</v>
       </c>
-      <c r="O9" t="s">
-        <v>207</v>
-      </c>
-      <c r="P9" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>208</v>
-      </c>
-      <c r="R9" t="s">
-        <v>208</v>
-      </c>
-      <c r="S9" t="s">
-        <v>207</v>
-      </c>
-      <c r="T9" t="s">
-        <v>208</v>
-      </c>
-      <c r="U9" t="s">
-        <v>208</v>
-      </c>
-      <c r="V9" t="s">
-        <v>208</v>
-      </c>
-      <c r="W9" t="s">
-        <v>208</v>
-      </c>
-      <c r="X9" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z9">
-        <v>9</v>
-      </c>
-      <c r="AA9">
+      <c r="AB9">
+        <v>4</v>
+      </c>
+      <c r="AC9">
+        <v>3</v>
+      </c>
+      <c r="AD9">
         <v>7</v>
       </c>
-      <c r="AB9">
+      <c r="AE9">
+        <v>7</v>
+      </c>
+      <c r="AF9">
         <v>6</v>
       </c>
-      <c r="AC9">
-        <v>5</v>
-      </c>
-      <c r="AD9">
-        <v>5</v>
-      </c>
-      <c r="AE9">
-        <v>6</v>
-      </c>
-      <c r="AF9">
-        <v>7</v>
-      </c>
       <c r="AG9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK9" t="s">
         <v>207</v>
       </c>
       <c r="AL9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AP9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT9" t="s">
         <v>207</v>
       </c>
       <c r="AU9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AW9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AX9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:50">
@@ -2510,25 +2507,25 @@
         <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H10" t="s">
         <v>163</v>
       </c>
       <c r="I10">
-        <v>23934</v>
+        <v>10189</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="L10" t="s">
         <v>166</v>
@@ -2537,115 +2534,115 @@
         <v>178</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="T10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AA10">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AB10">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AC10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE10">
         <v>6</v>
       </c>
       <c r="AF10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN10">
         <v>2</v>
       </c>
       <c r="AO10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT10" t="s">
         <v>207</v>
       </c>
       <c r="AU10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AW10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AX10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:50">
@@ -2662,25 +2659,25 @@
         <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H11" t="s">
         <v>163</v>
       </c>
       <c r="I11">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L11" t="s">
         <v>165</v>
@@ -2689,115 +2686,115 @@
         <v>179</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="O11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z11">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AB11">
+        <v>12</v>
+      </c>
+      <c r="AC11">
         <v>10</v>
-      </c>
-      <c r="AC11">
-        <v>8</v>
       </c>
       <c r="AD11">
         <v>6</v>
       </c>
       <c r="AE11">
+        <v>5</v>
+      </c>
+      <c r="AF11">
         <v>6</v>
       </c>
-      <c r="AF11">
-        <v>5</v>
-      </c>
       <c r="AG11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP11">
         <v>3</v>
       </c>
       <c r="AQ11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AS11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AW11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AX11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:50">
@@ -2814,10 +2811,10 @@
         <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G12" t="s">
         <v>162</v>
@@ -2826,100 +2823,100 @@
         <v>163</v>
       </c>
       <c r="I12">
-        <v>152</v>
+        <v>617</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="L12" t="s">
         <v>165</v>
       </c>
       <c r="M12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W12" t="s">
         <v>207</v>
       </c>
       <c r="X12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z12">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>6</v>
       </c>
       <c r="AE12">
+        <v>5</v>
+      </c>
+      <c r="AF12">
         <v>6</v>
       </c>
-      <c r="AF12">
-        <v>7</v>
-      </c>
       <c r="AG12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
         <v>2</v>
@@ -2928,7 +2925,7 @@
         <v>2</v>
       </c>
       <c r="AQ12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR12" t="s">
         <v>207</v>
@@ -2937,19 +2934,19 @@
         <v>207</v>
       </c>
       <c r="AT12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AW12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:50">
@@ -2966,142 +2963,142 @@
         <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F13">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H13" t="s">
         <v>163</v>
       </c>
       <c r="I13">
-        <v>888</v>
+        <v>468</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L13" t="s">
         <v>165</v>
       </c>
       <c r="M13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="O13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q13" t="s">
         <v>207</v>
       </c>
       <c r="R13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AA13">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC13">
+        <v>9</v>
+      </c>
+      <c r="AD13">
         <v>4</v>
-      </c>
-      <c r="AD13">
-        <v>5</v>
       </c>
       <c r="AE13">
         <v>6</v>
       </c>
       <c r="AF13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL13" t="s">
         <v>207</v>
       </c>
       <c r="AM13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN13">
         <v>2</v>
       </c>
       <c r="AO13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP13">
         <v>2</v>
       </c>
       <c r="AQ13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS13" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AT13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AW13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AX13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:50">
@@ -3118,109 +3115,109 @@
         <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H14" t="s">
         <v>163</v>
       </c>
       <c r="I14">
-        <v>121</v>
+        <v>474</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L14" t="s">
         <v>164</v>
       </c>
       <c r="M14" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="O14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA14">
+        <v>9</v>
+      </c>
+      <c r="AB14">
         <v>8</v>
       </c>
-      <c r="AB14">
+      <c r="AC14">
+        <v>6</v>
+      </c>
+      <c r="AD14">
         <v>7</v>
       </c>
-      <c r="AC14">
-        <v>5</v>
-      </c>
-      <c r="AD14">
+      <c r="AE14">
         <v>6</v>
       </c>
-      <c r="AE14">
-        <v>5</v>
-      </c>
       <c r="AF14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK14" t="s">
         <v>207</v>
       </c>
       <c r="AL14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN14">
         <v>2</v>
@@ -3229,31 +3226,31 @@
         <v>2</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AT14" t="s">
         <v>207</v>
       </c>
       <c r="AU14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AW14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AX14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:50">
@@ -3270,79 +3267,79 @@
         <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H15" t="s">
         <v>163</v>
       </c>
       <c r="I15">
-        <v>843</v>
+        <v>295</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="L15" t="s">
         <v>167</v>
       </c>
       <c r="M15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z15">
+        <v>12</v>
+      </c>
+      <c r="AA15">
+        <v>9</v>
+      </c>
+      <c r="AB15">
         <v>7</v>
       </c>
-      <c r="AA15">
+      <c r="AC15">
         <v>6</v>
-      </c>
-      <c r="AB15">
-        <v>5</v>
-      </c>
-      <c r="AC15">
-        <v>4</v>
       </c>
       <c r="AD15">
         <v>6</v>
@@ -3351,61 +3348,61 @@
         <v>6</v>
       </c>
       <c r="AF15">
+        <v>4</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN15">
         <v>3</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK15" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN15">
-        <v>2</v>
       </c>
       <c r="AO15">
         <v>3</v>
       </c>
       <c r="AP15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AT15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AW15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:50">
@@ -3425,139 +3422,139 @@
         <v>159</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H16" t="s">
         <v>163</v>
       </c>
       <c r="I16">
-        <v>280</v>
+        <v>477</v>
       </c>
       <c r="J16">
         <v>1</v>
       </c>
       <c r="K16">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L16" t="s">
         <v>165</v>
       </c>
       <c r="M16" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="O16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W16" t="s">
         <v>207</v>
       </c>
       <c r="X16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z16">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AA16">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AB16">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AC16">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AD16">
         <v>6</v>
       </c>
       <c r="AE16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF16">
         <v>6</v>
       </c>
       <c r="AG16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL16" t="s">
         <v>207</v>
       </c>
       <c r="AM16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AW16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AX16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:50">
@@ -3577,139 +3574,139 @@
         <v>160</v>
       </c>
       <c r="F17">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H17" t="s">
         <v>163</v>
       </c>
       <c r="I17">
-        <v>666</v>
+        <v>546</v>
       </c>
       <c r="J17">
         <v>1</v>
       </c>
       <c r="K17">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="L17" t="s">
         <v>165</v>
       </c>
       <c r="M17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="O17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V17" t="s">
         <v>207</v>
       </c>
       <c r="W17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z17">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA17">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE17">
+        <v>7</v>
+      </c>
+      <c r="AF17">
+        <v>7</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>207</v>
+      </c>
+      <c r="AN17">
+        <v>3</v>
+      </c>
+      <c r="AO17">
         <v>4</v>
       </c>
-      <c r="AF17">
-        <v>4</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN17">
-        <v>1</v>
-      </c>
-      <c r="AO17">
-        <v>2</v>
-      </c>
       <c r="AP17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AQ17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR17" t="s">
         <v>207</v>
       </c>
       <c r="AS17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AT17" t="s">
         <v>207</v>
       </c>
       <c r="AU17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AW17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AX17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:50">
@@ -3726,142 +3723,142 @@
         <v>124</v>
       </c>
       <c r="E18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H18" t="s">
         <v>163</v>
       </c>
       <c r="I18">
-        <v>783</v>
+        <v>153</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="L18" t="s">
         <v>165</v>
       </c>
       <c r="M18" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="O18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q18" t="s">
         <v>207</v>
       </c>
       <c r="R18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AC18">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE18">
+        <v>7</v>
+      </c>
+      <c r="AF18">
         <v>6</v>
       </c>
-      <c r="AF18">
-        <v>7</v>
-      </c>
       <c r="AG18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ18" t="s">
         <v>207</v>
       </c>
       <c r="AK18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO18">
         <v>3</v>
       </c>
       <c r="AP18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS18" t="s">
         <v>207</v>
       </c>
       <c r="AT18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AW18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AX18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:50">
@@ -3878,10 +3875,10 @@
         <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G19" t="s">
         <v>161</v>
@@ -3890,130 +3887,130 @@
         <v>163</v>
       </c>
       <c r="I19">
-        <v>322</v>
+        <v>247</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="K19">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="L19" t="s">
         <v>164</v>
       </c>
       <c r="M19" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="N19">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="O19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X19" t="s">
         <v>207</v>
       </c>
       <c r="Y19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z19">
+        <v>12</v>
+      </c>
+      <c r="AA19">
+        <v>10</v>
+      </c>
+      <c r="AB19">
         <v>8</v>
       </c>
-      <c r="AA19">
-        <v>6</v>
-      </c>
-      <c r="AB19">
-        <v>5</v>
-      </c>
       <c r="AC19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AD19">
         <v>6</v>
       </c>
       <c r="AE19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK19" t="s">
         <v>207</v>
       </c>
       <c r="AL19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN19">
         <v>3</v>
       </c>
       <c r="AO19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AU19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AW19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AX19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:50">
@@ -4033,139 +4030,139 @@
         <v>159</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H20" t="s">
         <v>163</v>
       </c>
       <c r="I20">
-        <v>574</v>
+        <v>124</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="L20" t="s">
         <v>166</v>
       </c>
       <c r="M20" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>206</v>
+      </c>
+      <c r="P20" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>206</v>
+      </c>
+      <c r="R20" t="s">
+        <v>207</v>
+      </c>
+      <c r="S20" t="s">
+        <v>206</v>
+      </c>
+      <c r="T20" t="s">
+        <v>207</v>
+      </c>
+      <c r="U20" t="s">
+        <v>207</v>
+      </c>
+      <c r="V20" t="s">
+        <v>207</v>
+      </c>
+      <c r="W20" t="s">
+        <v>206</v>
+      </c>
+      <c r="X20" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z20">
+        <v>14</v>
+      </c>
+      <c r="AA20">
+        <v>3</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
-      </c>
-      <c r="O20" t="s">
-        <v>207</v>
-      </c>
-      <c r="P20" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>207</v>
-      </c>
-      <c r="R20" t="s">
-        <v>208</v>
-      </c>
-      <c r="S20" t="s">
-        <v>207</v>
-      </c>
-      <c r="T20" t="s">
-        <v>208</v>
-      </c>
-      <c r="U20" t="s">
-        <v>208</v>
-      </c>
-      <c r="V20" t="s">
-        <v>208</v>
-      </c>
-      <c r="W20" t="s">
-        <v>207</v>
-      </c>
-      <c r="X20" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z20">
-        <v>10</v>
-      </c>
-      <c r="AA20">
-        <v>2</v>
-      </c>
-      <c r="AB20">
-        <v>1</v>
       </c>
       <c r="AC20">
         <v>0</v>
       </c>
       <c r="AD20">
+        <v>6</v>
+      </c>
+      <c r="AE20">
+        <v>4</v>
+      </c>
+      <c r="AF20">
         <v>7</v>
       </c>
-      <c r="AE20">
+      <c r="AG20" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN20">
+        <v>7</v>
+      </c>
+      <c r="AO20">
+        <v>7</v>
+      </c>
+      <c r="AP20">
         <v>6</v>
       </c>
-      <c r="AF20">
-        <v>6</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM20" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN20">
-        <v>5</v>
-      </c>
-      <c r="AO20">
-        <v>6</v>
-      </c>
-      <c r="AP20">
-        <v>4</v>
-      </c>
       <c r="AQ20" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AW20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AX20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:50">
@@ -4185,7 +4182,7 @@
         <v>160</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G21" t="s">
         <v>161</v>
@@ -4194,13 +4191,13 @@
         <v>163</v>
       </c>
       <c r="I21">
-        <v>250</v>
+        <v>647</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="K21">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="L21" t="s">
         <v>166</v>
@@ -4209,43 +4206,43 @@
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="V21" t="s">
         <v>207</v>
       </c>
       <c r="W21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB21">
         <v>2</v>
@@ -4260,61 +4257,61 @@
         <v>7</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG21" t="s">
         <v>207</v>
       </c>
       <c r="AH21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN21">
         <v>6</v>
       </c>
       <c r="AO21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP21">
         <v>6</v>
       </c>
       <c r="AQ21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AS21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AW21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AX21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:50">
@@ -4334,7 +4331,7 @@
         <v>160</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
         <v>161</v>
@@ -4343,130 +4340,130 @@
         <v>163</v>
       </c>
       <c r="I22">
-        <v>676</v>
+        <v>245</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="K22">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="L22" t="s">
         <v>166</v>
       </c>
       <c r="M22" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V22" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="W22" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z22">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA22">
+        <v>4</v>
+      </c>
+      <c r="AB22">
         <v>3</v>
-      </c>
-      <c r="AB22">
-        <v>2</v>
       </c>
       <c r="AC22">
         <v>1</v>
       </c>
       <c r="AD22">
+        <v>5</v>
+      </c>
+      <c r="AE22">
         <v>6</v>
       </c>
-      <c r="AE22">
-        <v>5</v>
-      </c>
       <c r="AF22">
+        <v>7</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN22">
+        <v>5</v>
+      </c>
+      <c r="AO22">
+        <v>5</v>
+      </c>
+      <c r="AP22">
         <v>6</v>
       </c>
-      <c r="AG22" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH22" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI22" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL22" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM22" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN22">
-        <v>5</v>
-      </c>
-      <c r="AO22">
-        <v>4</v>
-      </c>
-      <c r="AP22">
-        <v>4</v>
-      </c>
       <c r="AQ22" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AS22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AW22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AX22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:50">
@@ -4483,139 +4480,142 @@
         <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H23" t="s">
         <v>163</v>
       </c>
       <c r="I23">
-        <v>178</v>
+        <v>334</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="L23" t="s">
         <v>165</v>
       </c>
+      <c r="M23" t="s">
+        <v>186</v>
+      </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W23" t="s">
         <v>207</v>
       </c>
       <c r="X23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA23">
+        <v>3</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>1</v>
       </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
       <c r="AD23">
         <v>5</v>
       </c>
       <c r="AE23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO23">
         <v>6</v>
       </c>
       <c r="AP23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AW23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AX23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24" spans="1:50">
@@ -4632,139 +4632,142 @@
         <v>130</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H24" t="s">
         <v>163</v>
       </c>
       <c r="I24">
-        <v>448</v>
+        <v>120</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L24" t="s">
         <v>167</v>
       </c>
+      <c r="M24" t="s">
+        <v>180</v>
+      </c>
       <c r="N24">
+        <v>17</v>
+      </c>
+      <c r="O24" t="s">
+        <v>206</v>
+      </c>
+      <c r="P24" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>206</v>
+      </c>
+      <c r="R24" t="s">
+        <v>207</v>
+      </c>
+      <c r="S24" t="s">
+        <v>206</v>
+      </c>
+      <c r="T24" t="s">
+        <v>207</v>
+      </c>
+      <c r="U24" t="s">
+        <v>207</v>
+      </c>
+      <c r="V24" t="s">
+        <v>206</v>
+      </c>
+      <c r="W24" t="s">
+        <v>206</v>
+      </c>
+      <c r="X24" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z24">
+        <v>7</v>
+      </c>
+      <c r="AA24">
+        <v>2</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
         <v>0</v>
       </c>
-      <c r="O24" t="s">
-        <v>207</v>
-      </c>
-      <c r="P24" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>207</v>
-      </c>
-      <c r="R24" t="s">
-        <v>208</v>
-      </c>
-      <c r="S24" t="s">
-        <v>207</v>
-      </c>
-      <c r="T24" t="s">
-        <v>208</v>
-      </c>
-      <c r="U24" t="s">
-        <v>208</v>
-      </c>
-      <c r="V24" t="s">
-        <v>208</v>
-      </c>
-      <c r="W24" t="s">
-        <v>207</v>
-      </c>
-      <c r="X24" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z24">
-        <v>16</v>
-      </c>
-      <c r="AA24">
-        <v>5</v>
-      </c>
-      <c r="AB24">
-        <v>4</v>
-      </c>
-      <c r="AC24">
-        <v>1</v>
-      </c>
       <c r="AD24">
+        <v>7</v>
+      </c>
+      <c r="AE24">
+        <v>7</v>
+      </c>
+      <c r="AF24">
+        <v>5</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN24">
+        <v>7</v>
+      </c>
+      <c r="AO24">
         <v>6</v>
-      </c>
-      <c r="AE24">
-        <v>5</v>
-      </c>
-      <c r="AF24">
-        <v>6</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN24">
-        <v>5</v>
-      </c>
-      <c r="AO24">
-        <v>7</v>
       </c>
       <c r="AP24">
         <v>7</v>
       </c>
       <c r="AQ24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR24" t="s">
         <v>207</v>
       </c>
       <c r="AS24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AW24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AX24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:50">
@@ -4784,7 +4787,7 @@
         <v>160</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" t="s">
         <v>162</v>
@@ -4793,55 +4796,52 @@
         <v>163</v>
       </c>
       <c r="I25">
-        <v>123</v>
+        <v>610</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L25" t="s">
         <v>166</v>
       </c>
-      <c r="M25" t="s">
-        <v>190</v>
-      </c>
       <c r="N25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V25" t="s">
         <v>207</v>
       </c>
       <c r="W25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z25">
         <v>13</v>
@@ -4856,67 +4856,67 @@
         <v>1</v>
       </c>
       <c r="AD25">
+        <v>4</v>
+      </c>
+      <c r="AE25">
+        <v>5</v>
+      </c>
+      <c r="AF25">
         <v>7</v>
       </c>
-      <c r="AE25">
-        <v>4</v>
-      </c>
-      <c r="AF25">
-        <v>4</v>
-      </c>
       <c r="AG25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN25">
         <v>6</v>
       </c>
       <c r="AO25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AR25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS25" t="s">
         <v>207</v>
       </c>
       <c r="AT25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AW25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AX25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" spans="1:50">
@@ -4933,139 +4933,142 @@
         <v>132</v>
       </c>
       <c r="E26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H26" t="s">
         <v>163</v>
       </c>
       <c r="I26">
-        <v>373</v>
+        <v>262</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="L26" t="s">
         <v>166</v>
       </c>
+      <c r="M26" t="s">
+        <v>187</v>
+      </c>
       <c r="N26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V26" t="s">
         <v>207</v>
       </c>
       <c r="W26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AA26">
+        <v>5</v>
+      </c>
+      <c r="AB26">
         <v>3</v>
-      </c>
-      <c r="AB26">
-        <v>2</v>
       </c>
       <c r="AC26">
         <v>1</v>
       </c>
       <c r="AD26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE26">
+        <v>6</v>
+      </c>
+      <c r="AF26">
+        <v>5</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN26">
         <v>4</v>
-      </c>
-      <c r="AF26">
-        <v>4</v>
-      </c>
-      <c r="AG26" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH26" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI26" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL26" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM26" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN26">
-        <v>6</v>
       </c>
       <c r="AO26">
         <v>7</v>
       </c>
       <c r="AP26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ26" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AR26" t="s">
         <v>207</v>
       </c>
       <c r="AS26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AW26" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AX26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="1:50">
@@ -5085,49 +5088,52 @@
         <v>160</v>
       </c>
       <c r="F27">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H27" t="s">
         <v>163</v>
       </c>
       <c r="I27">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="K27">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L27" t="s">
         <v>166</v>
       </c>
+      <c r="M27" t="s">
+        <v>188</v>
+      </c>
       <c r="N27">
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V27" t="s">
         <v>207</v>
@@ -5136,85 +5142,85 @@
         <v>207</v>
       </c>
       <c r="X27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z27">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AA27">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC27">
         <v>1</v>
       </c>
       <c r="AD27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE27">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AH27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO27">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AP27">
         <v>5</v>
       </c>
       <c r="AQ27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AS27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AW27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AX27" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:50">
@@ -5234,7 +5240,7 @@
         <v>158</v>
       </c>
       <c r="F28">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G28" t="s">
         <v>162</v>
@@ -5243,64 +5249,61 @@
         <v>163</v>
       </c>
       <c r="I28">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="J28">
         <v>1</v>
       </c>
       <c r="K28">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="L28" t="s">
         <v>165</v>
       </c>
-      <c r="M28" t="s">
-        <v>191</v>
-      </c>
       <c r="N28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U28" t="s">
         <v>207</v>
       </c>
       <c r="V28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z28">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AA28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC28">
         <v>1</v>
@@ -5309,64 +5312,64 @@
         <v>6</v>
       </c>
       <c r="AE28">
+        <v>5</v>
+      </c>
+      <c r="AF28">
+        <v>5</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>206</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN28">
+        <v>5</v>
+      </c>
+      <c r="AO28">
+        <v>5</v>
+      </c>
+      <c r="AP28">
         <v>7</v>
       </c>
-      <c r="AF28">
-        <v>5</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI28" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK28" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL28" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM28" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN28">
-        <v>6</v>
-      </c>
-      <c r="AO28">
-        <v>7</v>
-      </c>
-      <c r="AP28">
-        <v>5</v>
-      </c>
       <c r="AQ28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR28" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AW28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AX28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:50">
@@ -5383,139 +5386,142 @@
         <v>135</v>
       </c>
       <c r="E29" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F29">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H29" t="s">
         <v>163</v>
       </c>
       <c r="I29">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="J29">
         <v>1</v>
       </c>
       <c r="K29">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L29" t="s">
         <v>167</v>
       </c>
+      <c r="M29" t="s">
+        <v>189</v>
+      </c>
       <c r="N29">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W29" t="s">
         <v>207</v>
       </c>
       <c r="X29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z29">
         <v>15</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AB29">
+        <v>2</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
         <v>6</v>
       </c>
-      <c r="AC29">
-        <v>3</v>
-      </c>
-      <c r="AD29">
-        <v>7</v>
-      </c>
       <c r="AE29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF29">
         <v>7</v>
       </c>
       <c r="AG29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN29">
         <v>6</v>
       </c>
       <c r="AO29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR29" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV29" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AW29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AX29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:50">
@@ -5535,7 +5541,7 @@
         <v>158</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
         <v>161</v>
@@ -5544,58 +5550,58 @@
         <v>163</v>
       </c>
       <c r="I30">
-        <v>807</v>
+        <v>412</v>
       </c>
       <c r="J30">
         <v>1</v>
       </c>
       <c r="K30">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L30" t="s">
         <v>166</v>
       </c>
       <c r="M30" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q30" t="s">
         <v>207</v>
       </c>
       <c r="R30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y30" t="s">
         <v>207</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>2</v>
@@ -5604,70 +5610,70 @@
         <v>2</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD30">
+        <v>7</v>
+      </c>
+      <c r="AE30">
+        <v>5</v>
+      </c>
+      <c r="AF30">
         <v>6</v>
       </c>
-      <c r="AE30">
-        <v>5</v>
-      </c>
-      <c r="AF30">
-        <v>7</v>
-      </c>
       <c r="AG30" t="s">
         <v>207</v>
       </c>
       <c r="AH30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN30">
+        <v>5</v>
+      </c>
+      <c r="AO30">
+        <v>4</v>
+      </c>
+      <c r="AP30">
         <v>3</v>
       </c>
-      <c r="AO30">
-        <v>2</v>
-      </c>
-      <c r="AP30">
-        <v>5</v>
-      </c>
       <c r="AQ30" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AR30" t="s">
         <v>207</v>
       </c>
       <c r="AS30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AW30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AX30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:50">
@@ -5684,7 +5690,7 @@
         <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F31">
         <v>16</v>
@@ -5696,61 +5702,61 @@
         <v>163</v>
       </c>
       <c r="I31">
-        <v>836</v>
+        <v>965</v>
       </c>
       <c r="J31">
         <v>1</v>
       </c>
       <c r="K31">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L31" t="s">
         <v>165</v>
       </c>
       <c r="M31" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y31" t="s">
         <v>207</v>
       </c>
       <c r="Z31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB31">
         <v>3</v>
@@ -5759,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="AD31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE31">
         <v>5</v>
@@ -5768,58 +5774,58 @@
         <v>6</v>
       </c>
       <c r="AG31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ31" t="s">
         <v>207</v>
       </c>
       <c r="AK31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN31">
+        <v>5</v>
+      </c>
+      <c r="AO31">
+        <v>7</v>
+      </c>
+      <c r="AP31">
         <v>4</v>
       </c>
-      <c r="AO31">
-        <v>5</v>
-      </c>
-      <c r="AP31">
-        <v>5</v>
-      </c>
       <c r="AQ31" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AR31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AW31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AX31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" spans="1:50">
@@ -5836,10 +5842,10 @@
         <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F32">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G32" t="s">
         <v>161</v>
@@ -5848,130 +5854,130 @@
         <v>163</v>
       </c>
       <c r="I32">
-        <v>509</v>
+        <v>1083</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L32" t="s">
         <v>164</v>
       </c>
       <c r="M32" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X32" t="s">
         <v>207</v>
       </c>
       <c r="Y32" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z32">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AA32">
+        <v>3</v>
+      </c>
+      <c r="AB32">
+        <v>2</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>6</v>
+      </c>
+      <c r="AE32">
         <v>7</v>
       </c>
-      <c r="AB32">
-        <v>5</v>
-      </c>
-      <c r="AC32">
-        <v>2</v>
-      </c>
-      <c r="AD32">
-        <v>7</v>
-      </c>
-      <c r="AE32">
+      <c r="AF32">
         <v>6</v>
       </c>
-      <c r="AF32">
-        <v>7</v>
-      </c>
       <c r="AG32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP32">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AQ32" t="s">
         <v>207</v>
       </c>
       <c r="AR32" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV32" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AW32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AX32" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:50">
@@ -5988,10 +5994,10 @@
         <v>139</v>
       </c>
       <c r="E33" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
         <v>161</v>
@@ -6000,7 +6006,7 @@
         <v>163</v>
       </c>
       <c r="I33">
-        <v>616</v>
+        <v>967</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -6012,46 +6018,46 @@
         <v>167</v>
       </c>
       <c r="M33" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q33" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>2</v>
@@ -6060,70 +6066,70 @@
         <v>1</v>
       </c>
       <c r="AC33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE33">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AF33">
         <v>5</v>
       </c>
       <c r="AG33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN33">
         <v>4</v>
       </c>
       <c r="AO33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR33" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS33" t="s">
         <v>207</v>
       </c>
       <c r="AT33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AW33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AX33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="34" spans="1:50">
@@ -6140,142 +6146,142 @@
         <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F34">
         <v>12</v>
       </c>
       <c r="G34" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H34" t="s">
         <v>163</v>
       </c>
       <c r="I34">
-        <v>475</v>
+        <v>1427</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="L34" t="s">
         <v>166</v>
       </c>
       <c r="M34" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y34" t="s">
         <v>207</v>
       </c>
       <c r="Z34">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC34">
         <v>1</v>
       </c>
       <c r="AD34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE34">
+        <v>7</v>
+      </c>
+      <c r="AF34">
         <v>6</v>
       </c>
-      <c r="AF34">
-        <v>4</v>
-      </c>
       <c r="AG34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI34" t="s">
         <v>207</v>
       </c>
       <c r="AJ34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN34">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ34" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AR34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS34" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AT34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU34" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AW34" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AX34" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:50">
@@ -6295,67 +6301,67 @@
         <v>158</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H35" t="s">
         <v>163</v>
       </c>
       <c r="I35">
-        <v>904</v>
+        <v>295</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="L35" t="s">
         <v>165</v>
       </c>
       <c r="M35" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q35" t="s">
         <v>207</v>
       </c>
       <c r="R35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35">
         <v>3</v>
@@ -6367,67 +6373,67 @@
         <v>1</v>
       </c>
       <c r="AD35">
+        <v>5</v>
+      </c>
+      <c r="AE35">
+        <v>6</v>
+      </c>
+      <c r="AF35">
+        <v>6</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN35">
         <v>4</v>
       </c>
-      <c r="AE35">
-        <v>5</v>
-      </c>
-      <c r="AF35">
-        <v>7</v>
-      </c>
-      <c r="AG35" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK35" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL35" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM35" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN35">
-        <v>5</v>
-      </c>
       <c r="AO35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AQ35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AS35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AW35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AX35" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:50">
@@ -6444,10 +6450,10 @@
         <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F36">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G36" t="s">
         <v>162</v>
@@ -6456,13 +6462,13 @@
         <v>163</v>
       </c>
       <c r="I36">
-        <v>220</v>
+        <v>283</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L36" t="s">
         <v>167</v>
@@ -6471,22 +6477,22 @@
         <v>0</v>
       </c>
       <c r="O36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U36" t="s">
         <v>207</v>
@@ -6495,25 +6501,25 @@
         <v>207</v>
       </c>
       <c r="W36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AB36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD36">
         <v>3</v>
@@ -6522,61 +6528,61 @@
         <v>3</v>
       </c>
       <c r="AF36">
+        <v>4</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN36">
         <v>3</v>
       </c>
-      <c r="AG36" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM36" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN36">
-        <v>5</v>
-      </c>
       <c r="AO36">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AP36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT36" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AU36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AW36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AX36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:50">
@@ -6593,10 +6599,10 @@
         <v>143</v>
       </c>
       <c r="E37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G37" t="s">
         <v>161</v>
@@ -6605,13 +6611,13 @@
         <v>163</v>
       </c>
       <c r="I37">
-        <v>215</v>
+        <v>501</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="L37" t="s">
         <v>167</v>
@@ -6620,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="O37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P37" t="s">
         <v>207</v>
@@ -6629,82 +6635,82 @@
         <v>207</v>
       </c>
       <c r="R37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="V37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA37">
         <v>5</v>
       </c>
       <c r="AB37">
+        <v>4</v>
+      </c>
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AD37">
+        <v>4</v>
+      </c>
+      <c r="AE37">
         <v>3</v>
       </c>
-      <c r="AC37">
+      <c r="AF37">
         <v>2</v>
       </c>
-      <c r="AD37">
-        <v>3</v>
-      </c>
-      <c r="AE37">
-        <v>5</v>
-      </c>
-      <c r="AF37">
-        <v>3</v>
-      </c>
       <c r="AG37" t="s">
         <v>207</v>
       </c>
       <c r="AH37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO37">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AP37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ37" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR37" t="s">
         <v>207</v>
@@ -6713,19 +6719,19 @@
         <v>207</v>
       </c>
       <c r="AT37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AW37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AX37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:50">
@@ -6742,25 +6748,25 @@
         <v>144</v>
       </c>
       <c r="E38" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F38">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H38" t="s">
         <v>163</v>
       </c>
       <c r="I38">
-        <v>483</v>
+        <v>360</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L38" t="s">
         <v>168</v>
@@ -6769,22 +6775,22 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q38" t="s">
         <v>207</v>
       </c>
       <c r="R38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U38" t="s">
         <v>207</v>
@@ -6793,88 +6799,88 @@
         <v>207</v>
       </c>
       <c r="W38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC38">
         <v>3</v>
       </c>
       <c r="AD38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE38">
         <v>3</v>
       </c>
       <c r="AF38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN38">
         <v>5</v>
       </c>
       <c r="AO38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR38" t="s">
         <v>207</v>
       </c>
       <c r="AS38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AW38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AX38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:50">
@@ -6891,37 +6897,34 @@
         <v>145</v>
       </c>
       <c r="E39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F39">
         <v>3</v>
       </c>
       <c r="G39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H39" t="s">
         <v>163</v>
       </c>
       <c r="I39">
-        <v>268</v>
+        <v>395</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L39" t="s">
         <v>168</v>
       </c>
-      <c r="M39" t="s">
-        <v>192</v>
-      </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P39" t="s">
         <v>207</v>
@@ -6930,31 +6933,31 @@
         <v>207</v>
       </c>
       <c r="R39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z39">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA39">
         <v>3</v>
@@ -6963,37 +6966,37 @@
         <v>2</v>
       </c>
       <c r="AC39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD39">
+        <v>5</v>
+      </c>
+      <c r="AE39">
         <v>4</v>
       </c>
-      <c r="AE39">
+      <c r="AF39">
         <v>3</v>
       </c>
-      <c r="AF39">
-        <v>4</v>
-      </c>
       <c r="AG39" t="s">
         <v>207</v>
       </c>
       <c r="AH39" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN39">
         <v>3</v>
@@ -7002,10 +7005,10 @@
         <v>3</v>
       </c>
       <c r="AP39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ39" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR39" t="s">
         <v>207</v>
@@ -7014,19 +7017,19 @@
         <v>207</v>
       </c>
       <c r="AT39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AW39" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AX39" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="40" spans="1:50">
@@ -7043,19 +7046,19 @@
         <v>146</v>
       </c>
       <c r="E40" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F40">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H40" t="s">
         <v>163</v>
       </c>
       <c r="I40">
-        <v>391</v>
+        <v>535</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -7067,46 +7070,46 @@
         <v>169</v>
       </c>
       <c r="M40" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P40" t="s">
         <v>207</v>
       </c>
       <c r="Q40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V40" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="W40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA40">
         <v>3</v>
@@ -7118,67 +7121,67 @@
         <v>1</v>
       </c>
       <c r="AD40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF40">
         <v>3</v>
       </c>
       <c r="AG40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH40" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AI40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AJ40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AK40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN40">
         <v>3</v>
       </c>
       <c r="AO40">
+        <v>3</v>
+      </c>
+      <c r="AP40">
         <v>2</v>
       </c>
-      <c r="AP40">
-        <v>4</v>
-      </c>
       <c r="AQ40" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR40" t="s">
         <v>207</v>
       </c>
       <c r="AS40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AT40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AW40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AX40" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" spans="1:50">
@@ -7195,25 +7198,25 @@
         <v>147</v>
       </c>
       <c r="E41" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F41">
         <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H41" t="s">
         <v>163</v>
       </c>
       <c r="I41">
-        <v>584</v>
+        <v>103</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="K41">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L41" t="s">
         <v>167</v>
@@ -7222,112 +7225,112 @@
         <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Q41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="W41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z41">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AB41">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC41">
+        <v>1</v>
+      </c>
+      <c r="AD41">
+        <v>1</v>
+      </c>
+      <c r="AE41">
+        <v>3</v>
+      </c>
+      <c r="AF41">
+        <v>5</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN41">
+        <v>3</v>
+      </c>
+      <c r="AO41">
+        <v>5</v>
+      </c>
+      <c r="AP41">
         <v>4</v>
       </c>
-      <c r="AD41">
-        <v>2</v>
-      </c>
-      <c r="AE41">
-        <v>2</v>
-      </c>
-      <c r="AF41">
-        <v>3</v>
-      </c>
-      <c r="AG41" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL41" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM41" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN41">
-        <v>5</v>
-      </c>
-      <c r="AO41">
-        <v>5</v>
-      </c>
-      <c r="AP41">
-        <v>3</v>
-      </c>
       <c r="AQ41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR41" t="s">
         <v>207</v>
       </c>
       <c r="AS41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AT41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AW41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AX41" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:50">
@@ -7344,10 +7347,10 @@
         <v>148</v>
       </c>
       <c r="E42" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F42">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
         <v>161</v>
@@ -7356,58 +7359,61 @@
         <v>163</v>
       </c>
       <c r="I42">
-        <v>165</v>
+        <v>301</v>
       </c>
       <c r="J42">
         <v>1</v>
       </c>
       <c r="K42">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L42" t="s">
         <v>167</v>
       </c>
+      <c r="M42" t="s">
+        <v>196</v>
+      </c>
       <c r="N42">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="W42" t="s">
         <v>207</v>
       </c>
       <c r="X42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z42">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB42">
         <v>2</v>
@@ -7419,43 +7425,43 @@
         <v>3</v>
       </c>
       <c r="AE42">
+        <v>1</v>
+      </c>
+      <c r="AF42">
+        <v>2</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>206</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN42">
         <v>4</v>
-      </c>
-      <c r="AF42">
-        <v>3</v>
-      </c>
-      <c r="AG42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM42" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN42">
-        <v>5</v>
       </c>
       <c r="AO42">
         <v>4</v>
       </c>
       <c r="AP42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR42" t="s">
         <v>207</v>
@@ -7464,19 +7470,19 @@
         <v>207</v>
       </c>
       <c r="AT42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AW42" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AX42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:50">
@@ -7493,70 +7499,70 @@
         <v>149</v>
       </c>
       <c r="E43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F43">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H43" t="s">
         <v>163</v>
       </c>
       <c r="I43">
-        <v>723</v>
+        <v>424</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="K43">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L43" t="s">
         <v>169</v>
       </c>
       <c r="M43" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="O43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U43" t="s">
         <v>207</v>
       </c>
       <c r="V43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W43" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="X43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA43">
         <v>3</v>
@@ -7568,67 +7574,67 @@
         <v>2</v>
       </c>
       <c r="AD43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO43">
         <v>4</v>
       </c>
       <c r="AP43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU43" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AV43" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AW43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AX43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:50">
@@ -7645,10 +7651,10 @@
         <v>150</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G44" t="s">
         <v>162</v>
@@ -7657,70 +7663,70 @@
         <v>163</v>
       </c>
       <c r="I44">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="J44">
         <v>1</v>
       </c>
       <c r="K44">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L44" t="s">
         <v>169</v>
       </c>
       <c r="M44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="O44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P44" t="s">
         <v>207</v>
       </c>
       <c r="Q44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W44" t="s">
         <v>207</v>
       </c>
       <c r="X44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z44">
+        <v>17</v>
+      </c>
+      <c r="AA44">
+        <v>11</v>
+      </c>
+      <c r="AB44">
+        <v>9</v>
+      </c>
+      <c r="AC44">
+        <v>7</v>
+      </c>
+      <c r="AD44">
         <v>6</v>
-      </c>
-      <c r="AA44">
-        <v>4</v>
-      </c>
-      <c r="AB44">
-        <v>3</v>
-      </c>
-      <c r="AC44">
-        <v>2</v>
-      </c>
-      <c r="AD44">
-        <v>7</v>
       </c>
       <c r="AE44">
         <v>5</v>
@@ -7729,58 +7735,58 @@
         <v>6</v>
       </c>
       <c r="AG44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AL44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AV44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AW44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AX44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:50">
@@ -7797,10 +7803,10 @@
         <v>151</v>
       </c>
       <c r="E45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
         <v>161</v>
@@ -7809,130 +7815,130 @@
         <v>163</v>
       </c>
       <c r="I45">
-        <v>231</v>
+        <v>816</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="K45">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L45" t="s">
         <v>169</v>
       </c>
       <c r="M45" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N45">
+        <v>77</v>
+      </c>
+      <c r="O45" t="s">
+        <v>206</v>
+      </c>
+      <c r="P45" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>207</v>
+      </c>
+      <c r="R45" t="s">
+        <v>207</v>
+      </c>
+      <c r="S45" t="s">
+        <v>206</v>
+      </c>
+      <c r="T45" t="s">
+        <v>207</v>
+      </c>
+      <c r="U45" t="s">
+        <v>207</v>
+      </c>
+      <c r="V45" t="s">
+        <v>207</v>
+      </c>
+      <c r="W45" t="s">
+        <v>206</v>
+      </c>
+      <c r="X45" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z45">
         <v>4</v>
       </c>
-      <c r="O45" t="s">
-        <v>207</v>
-      </c>
-      <c r="P45" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>208</v>
-      </c>
-      <c r="R45" t="s">
-        <v>208</v>
-      </c>
-      <c r="S45" t="s">
-        <v>207</v>
-      </c>
-      <c r="T45" t="s">
-        <v>208</v>
-      </c>
-      <c r="U45" t="s">
-        <v>208</v>
-      </c>
-      <c r="V45" t="s">
-        <v>208</v>
-      </c>
-      <c r="W45" t="s">
-        <v>207</v>
-      </c>
-      <c r="X45" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z45">
-        <v>9</v>
-      </c>
       <c r="AA45">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AB45">
+        <v>2</v>
+      </c>
+      <c r="AC45">
+        <v>1</v>
+      </c>
+      <c r="AD45">
+        <v>5</v>
+      </c>
+      <c r="AE45">
         <v>6</v>
       </c>
-      <c r="AC45">
+      <c r="AF45">
+        <v>6</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN45">
         <v>4</v>
       </c>
-      <c r="AD45">
-        <v>5</v>
-      </c>
-      <c r="AE45">
-        <v>7</v>
-      </c>
-      <c r="AF45">
-        <v>5</v>
-      </c>
-      <c r="AG45" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH45" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ45" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK45" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL45" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM45" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN45">
-        <v>3</v>
-      </c>
       <c r="AO45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU45" t="s">
         <v>207</v>
       </c>
       <c r="AV45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AW45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AX45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:50">
@@ -7949,10 +7955,10 @@
         <v>152</v>
       </c>
       <c r="E46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F46">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G46" t="s">
         <v>162</v>
@@ -7961,130 +7967,130 @@
         <v>163</v>
       </c>
       <c r="I46">
-        <v>952</v>
+        <v>391</v>
       </c>
       <c r="J46">
         <v>1</v>
       </c>
       <c r="K46">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L46" t="s">
         <v>165</v>
       </c>
       <c r="M46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="O46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P46" t="s">
         <v>207</v>
       </c>
       <c r="Q46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W46" t="s">
         <v>207</v>
       </c>
       <c r="X46" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z46">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AA46">
+        <v>9</v>
+      </c>
+      <c r="AB46">
+        <v>7</v>
+      </c>
+      <c r="AC46">
+        <v>4</v>
+      </c>
+      <c r="AD46">
+        <v>5</v>
+      </c>
+      <c r="AE46">
+        <v>4</v>
+      </c>
+      <c r="AF46">
         <v>6</v>
       </c>
-      <c r="AB46">
-        <v>5</v>
-      </c>
-      <c r="AC46">
+      <c r="AG46" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN46">
         <v>3</v>
-      </c>
-      <c r="AD46">
-        <v>6</v>
-      </c>
-      <c r="AE46">
-        <v>5</v>
-      </c>
-      <c r="AF46">
-        <v>5</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM46" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN46">
-        <v>4</v>
       </c>
       <c r="AO46">
         <v>4</v>
       </c>
       <c r="AP46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT46" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU46" t="s">
         <v>207</v>
       </c>
       <c r="AV46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AW46" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AX46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:50">
@@ -8104,7 +8110,7 @@
         <v>160</v>
       </c>
       <c r="F47">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G47" t="s">
         <v>161</v>
@@ -8113,7 +8119,7 @@
         <v>163</v>
       </c>
       <c r="I47">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -8125,52 +8131,52 @@
         <v>169</v>
       </c>
       <c r="M47" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="O47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V47" t="s">
         <v>207</v>
       </c>
       <c r="W47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z47">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AA47">
+        <v>10</v>
+      </c>
+      <c r="AB47">
         <v>8</v>
-      </c>
-      <c r="AB47">
-        <v>7</v>
       </c>
       <c r="AC47">
         <v>5</v>
@@ -8179,64 +8185,64 @@
         <v>4</v>
       </c>
       <c r="AE47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF47">
+        <v>5</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>207</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN47">
         <v>4</v>
-      </c>
-      <c r="AG47" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH47" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI47" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ47" t="s">
-        <v>207</v>
-      </c>
-      <c r="AK47" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL47" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM47" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN47">
-        <v>3</v>
       </c>
       <c r="AO47">
         <v>3</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AQ47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT47" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AU47" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AV47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AW47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AX47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:50">
@@ -8253,142 +8259,142 @@
         <v>154</v>
       </c>
       <c r="E48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G48" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H48" t="s">
         <v>163</v>
       </c>
       <c r="I48">
-        <v>2167</v>
+        <v>1148</v>
       </c>
       <c r="J48">
         <v>3</v>
       </c>
       <c r="K48">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="L48" t="s">
         <v>165</v>
       </c>
       <c r="M48" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N48">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="O48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P48" t="s">
         <v>207</v>
       </c>
       <c r="Q48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z48">
         <v>10</v>
       </c>
       <c r="AA48">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB48">
+        <v>2</v>
+      </c>
+      <c r="AC48">
+        <v>1</v>
+      </c>
+      <c r="AD48">
         <v>4</v>
-      </c>
-      <c r="AC48">
-        <v>2</v>
-      </c>
-      <c r="AD48">
-        <v>5</v>
       </c>
       <c r="AE48">
         <v>4</v>
       </c>
       <c r="AF48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN48">
         <v>3</v>
       </c>
       <c r="AO48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AQ48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR48" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AS48" t="s">
         <v>207</v>
       </c>
       <c r="AT48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AW48" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AX48" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:50">
@@ -8405,10 +8411,10 @@
         <v>155</v>
       </c>
       <c r="E49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F49">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
         <v>161</v>
@@ -8417,130 +8423,130 @@
         <v>163</v>
       </c>
       <c r="I49">
-        <v>2746</v>
+        <v>2733</v>
       </c>
       <c r="J49">
         <v>2</v>
       </c>
       <c r="K49">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L49" t="s">
         <v>165</v>
       </c>
       <c r="M49" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49" t="s">
+        <v>206</v>
+      </c>
+      <c r="P49" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>207</v>
+      </c>
+      <c r="R49" t="s">
+        <v>206</v>
+      </c>
+      <c r="S49" t="s">
+        <v>206</v>
+      </c>
+      <c r="T49" t="s">
+        <v>207</v>
+      </c>
+      <c r="U49" t="s">
+        <v>207</v>
+      </c>
+      <c r="V49" t="s">
+        <v>207</v>
+      </c>
+      <c r="W49" t="s">
+        <v>206</v>
+      </c>
+      <c r="X49" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z49">
+        <v>15</v>
+      </c>
+      <c r="AA49">
+        <v>6</v>
+      </c>
+      <c r="AB49">
+        <v>5</v>
+      </c>
+      <c r="AC49">
+        <v>2</v>
+      </c>
+      <c r="AD49">
         <v>4</v>
       </c>
-      <c r="O49" t="s">
-        <v>207</v>
-      </c>
-      <c r="P49" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>207</v>
-      </c>
-      <c r="R49" t="s">
-        <v>207</v>
-      </c>
-      <c r="S49" t="s">
-        <v>207</v>
-      </c>
-      <c r="T49" t="s">
-        <v>208</v>
-      </c>
-      <c r="U49" t="s">
-        <v>208</v>
-      </c>
-      <c r="V49" t="s">
-        <v>208</v>
-      </c>
-      <c r="W49" t="s">
-        <v>208</v>
-      </c>
-      <c r="X49" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y49" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z49">
+      <c r="AE49">
         <v>6</v>
       </c>
-      <c r="AA49">
-        <v>3</v>
-      </c>
-      <c r="AB49">
-        <v>2</v>
-      </c>
-      <c r="AC49">
-        <v>1</v>
-      </c>
-      <c r="AD49">
-        <v>3</v>
-      </c>
-      <c r="AE49">
-        <v>2</v>
-      </c>
       <c r="AF49">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AG49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AK49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AL49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP49">
         <v>4</v>
       </c>
       <c r="AQ49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AW49" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AX49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:50">
@@ -8557,97 +8563,97 @@
         <v>156</v>
       </c>
       <c r="E50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F50">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H50" t="s">
         <v>163</v>
       </c>
       <c r="I50">
-        <v>1955</v>
+        <v>1371</v>
       </c>
       <c r="J50">
         <v>3</v>
       </c>
       <c r="K50">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="L50" t="s">
         <v>168</v>
       </c>
       <c r="M50" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="S50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="V50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Z50">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC50">
         <v>1</v>
       </c>
       <c r="AD50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE50">
         <v>5</v>
       </c>
       <c r="AF50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AH50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ50" t="s">
         <v>207</v>
@@ -8656,43 +8662,43 @@
         <v>207</v>
       </c>
       <c r="AL50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AN50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP50">
         <v>4</v>
       </c>
       <c r="AQ50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AR50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS50" t="s">
         <v>207</v>
       </c>
       <c r="AT50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU50" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AW50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AX50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:50">
@@ -8709,142 +8715,142 @@
         <v>157</v>
       </c>
       <c r="E51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F51">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H51" t="s">
         <v>163</v>
       </c>
       <c r="I51">
-        <v>2493</v>
+        <v>2833</v>
       </c>
       <c r="J51">
         <v>2</v>
       </c>
       <c r="K51">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L51" t="s">
         <v>166</v>
       </c>
       <c r="M51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N51">
+        <v>43</v>
+      </c>
+      <c r="O51" t="s">
+        <v>206</v>
+      </c>
+      <c r="P51" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>207</v>
+      </c>
+      <c r="R51" t="s">
+        <v>206</v>
+      </c>
+      <c r="S51" t="s">
+        <v>206</v>
+      </c>
+      <c r="T51" t="s">
+        <v>207</v>
+      </c>
+      <c r="U51" t="s">
+        <v>207</v>
+      </c>
+      <c r="V51" t="s">
+        <v>206</v>
+      </c>
+      <c r="W51" t="s">
+        <v>207</v>
+      </c>
+      <c r="X51" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z51">
+        <v>14</v>
+      </c>
+      <c r="AA51">
+        <v>5</v>
+      </c>
+      <c r="AB51">
+        <v>4</v>
+      </c>
+      <c r="AC51">
+        <v>2</v>
+      </c>
+      <c r="AD51">
+        <v>5</v>
+      </c>
+      <c r="AE51">
+        <v>4</v>
+      </c>
+      <c r="AF51">
+        <v>5</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>207</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>207</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>206</v>
+      </c>
+      <c r="AM51" t="s">
+        <v>206</v>
+      </c>
+      <c r="AN51">
         <v>3</v>
-      </c>
-      <c r="O51" t="s">
-        <v>207</v>
-      </c>
-      <c r="P51" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>208</v>
-      </c>
-      <c r="R51" t="s">
-        <v>207</v>
-      </c>
-      <c r="S51" t="s">
-        <v>207</v>
-      </c>
-      <c r="T51" t="s">
-        <v>208</v>
-      </c>
-      <c r="U51" t="s">
-        <v>208</v>
-      </c>
-      <c r="V51" t="s">
-        <v>208</v>
-      </c>
-      <c r="W51" t="s">
-        <v>208</v>
-      </c>
-      <c r="X51" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z51">
-        <v>9</v>
-      </c>
-      <c r="AA51">
-        <v>3</v>
-      </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>1</v>
-      </c>
-      <c r="AD51">
-        <v>4</v>
-      </c>
-      <c r="AE51">
-        <v>5</v>
-      </c>
-      <c r="AF51">
-        <v>5</v>
-      </c>
-      <c r="AG51" t="s">
-        <v>208</v>
-      </c>
-      <c r="AH51" t="s">
-        <v>208</v>
-      </c>
-      <c r="AI51" t="s">
-        <v>208</v>
-      </c>
-      <c r="AJ51" t="s">
-        <v>208</v>
-      </c>
-      <c r="AK51" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL51" t="s">
-        <v>207</v>
-      </c>
-      <c r="AM51" t="s">
-        <v>207</v>
-      </c>
-      <c r="AN51">
-        <v>4</v>
       </c>
       <c r="AO51">
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ51" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AR51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AS51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AT51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AU51" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AV51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AW51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AX51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
